--- a/Agriculture/A2_Extra_Inputs/A-Xtra_Emissions.xlsx
+++ b/Agriculture/A2_Extra_Inputs/A-Xtra_Emissions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yds3\Downloads\AGR_20241223\A2_Extra_Inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://clgcr.sharepoint.com/sites/ClimateLeadGroup-NDC_Ecu/Documentos compartidos/ECU_NDC_model/lastest_models_2025_02_03/Agriculture/A2_Extra_Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2979922D-D140-4B89-A140-17BF54A3BCB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{2979922D-D140-4B89-A140-17BF54A3BCB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6D1C0A2-4E18-410C-9D61-8EB2B1A63D7D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1410" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GHGs" sheetId="1" r:id="rId1"/>
@@ -140,9 +140,6 @@
     <t>CO2e_GAN_FERM</t>
   </si>
   <si>
-    <t>Mton de gas/Mha</t>
-  </si>
-  <si>
     <t>CO2e_GAN_GED</t>
   </si>
   <si>
@@ -215,9 +212,6 @@
     <t>T5AVEGAN</t>
   </si>
   <si>
-    <t>Mton de Gas / MCabeza</t>
-  </si>
-  <si>
     <t>INGEI 2018</t>
   </si>
   <si>
@@ -315,6 +309,12 @@
   </si>
   <si>
     <t>T5PATGAN</t>
+  </si>
+  <si>
+    <t>Gg de Gas / MCabeza</t>
+  </si>
+  <si>
+    <t>Gg de Gas/Mha</t>
   </si>
 </sst>
 </file>
@@ -1089,7 +1089,7 @@
     <cellStyle name="Normal 2" xfId="4" xr:uid="{9A661356-CED7-4081-A7A9-B690E640B238}"/>
     <cellStyle name="Normal 3" xfId="2" xr:uid="{F5CC62F1-1C8C-48E3-A9EA-C456C8D15D2A}"/>
     <cellStyle name="Normal 4" xfId="7" xr:uid="{A6FE6838-5EF1-44C9-A7C9-34087389D241}"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
     <cellStyle name="Porcentaje 2" xfId="6" xr:uid="{D512FAB1-1F34-4E8B-901F-CE59BE013093}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1374,7 +1374,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G153"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.5546875" style="3" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" bestFit="1" customWidth="1"/>
@@ -1410,7 +1410,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="54" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>16</v>
@@ -1422,16 +1422,16 @@
         <v>13</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F2" s="50"/>
       <c r="G2" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>16</v>
@@ -1443,16 +1443,16 @@
         <v>13</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F3" s="50"/>
       <c r="G3" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>16</v>
@@ -1464,16 +1464,16 @@
         <v>13</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F4" s="50"/>
       <c r="G4" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>16</v>
@@ -1485,16 +1485,16 @@
         <v>13</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F5" s="50"/>
       <c r="G5" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>16</v>
@@ -1506,18 +1506,18 @@
         <v>13</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F6" s="68">
         <v>-9.6749297265415479E-2</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>16</v>
@@ -1529,18 +1529,18 @@
         <v>13</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F7" s="68">
         <v>-8.1812218770374215E-2</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" s="17" t="s">
         <v>16</v>
@@ -1552,18 +1552,18 @@
         <v>13</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F8" s="68">
         <v>-0.1486695470843373</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>16</v>
@@ -1575,21 +1575,21 @@
         <v>13</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F9" s="68">
         <v>-9.9961102922777587E-2</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="92" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C10" s="74">
         <v>1.06E-2</v>
@@ -1598,19 +1598,19 @@
         <v>13</v>
       </c>
       <c r="E10" s="52" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F10" s="66"/>
       <c r="G10" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C11" s="64">
         <v>1.06E-2</v>
@@ -1619,19 +1619,19 @@
         <v>13</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F11" s="66"/>
       <c r="G11" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="92" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C12" s="64">
         <v>1.06E-2</v>
@@ -1640,19 +1640,19 @@
         <v>13</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F12" s="49"/>
       <c r="G12" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="92" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C13" s="64">
         <v>1.06E-2</v>
@@ -1661,19 +1661,19 @@
         <v>13</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F13" s="50"/>
       <c r="G13" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="92" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C14" s="64">
         <v>1.06E-2</v>
@@ -1682,19 +1682,19 @@
         <v>13</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F14" s="50"/>
       <c r="G14" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="92" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C15" s="64">
         <v>1.06E-2</v>
@@ -1703,19 +1703,19 @@
         <v>13</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F15" s="38"/>
       <c r="G15" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="92" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C16" s="64">
         <v>1.06E-2</v>
@@ -1724,19 +1724,19 @@
         <v>13</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F16" s="38"/>
       <c r="G16" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="92" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C17" s="64">
         <v>1.06E-2</v>
@@ -1745,19 +1745,19 @@
         <v>13</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F17" s="50"/>
       <c r="G17" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="92" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B18" s="30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C18" s="64">
         <v>1.06E-2</v>
@@ -1766,19 +1766,19 @@
         <v>13</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F18" s="50"/>
       <c r="G18" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="92" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C19" s="64">
         <v>1.06E-2</v>
@@ -1787,19 +1787,19 @@
         <v>13</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F19" s="38"/>
       <c r="G19" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="92" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C20" s="64">
         <v>1.06E-2</v>
@@ -1808,19 +1808,19 @@
         <v>13</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F20" s="38"/>
       <c r="G20" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="92" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" s="30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C21" s="64">
         <v>1.06E-2</v>
@@ -1829,19 +1829,19 @@
         <v>13</v>
       </c>
       <c r="E21" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F21" s="38"/>
       <c r="G21" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="92" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B22" s="30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C22" s="64">
         <v>1.06E-2</v>
@@ -1850,19 +1850,19 @@
         <v>13</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F22" s="38"/>
       <c r="G22" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="58" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B23" s="59" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C23" s="67">
         <v>5.8999999999999999E-3</v>
@@ -1871,19 +1871,19 @@
         <v>13</v>
       </c>
       <c r="E23" s="61" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F23" s="50"/>
       <c r="G23" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C24" s="63">
         <v>5.8999999999999999E-3</v>
@@ -1892,19 +1892,19 @@
         <v>13</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F24" s="50"/>
       <c r="G24" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C25" s="63">
         <v>1.0059</v>
@@ -1913,19 +1913,19 @@
         <v>13</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F25" s="50"/>
       <c r="G25" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C26" s="63">
         <v>2.0059</v>
@@ -1934,19 +1934,19 @@
         <v>13</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F26" s="50"/>
       <c r="G26" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C27" s="63">
         <v>3.0059</v>
@@ -1955,19 +1955,19 @@
         <v>13</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F27" s="38"/>
       <c r="G27" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C28" s="63">
         <v>5.8999999999999999E-3</v>
@@ -1976,19 +1976,19 @@
         <v>13</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F28" s="38"/>
       <c r="G28" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C29" s="63">
         <v>5.8999999999999999E-3</v>
@@ -1997,19 +1997,19 @@
         <v>13</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F29" s="38"/>
       <c r="G29" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C30" s="63">
         <v>5.8999999999999999E-3</v>
@@ -2018,19 +2018,19 @@
         <v>13</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F30" s="38"/>
       <c r="G30" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C31" s="63">
         <v>5.8999999999999999E-3</v>
@@ -2039,19 +2039,19 @@
         <v>13</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F31" s="38"/>
       <c r="G31" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="92" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B32" s="35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C32" s="35">
         <v>2E-3</v>
@@ -2060,19 +2060,19 @@
         <v>13</v>
       </c>
       <c r="E32" s="52" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F32" s="50"/>
       <c r="G32" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="92" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B33" s="30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C33" s="30">
         <v>2E-3</v>
@@ -2081,19 +2081,19 @@
         <v>13</v>
       </c>
       <c r="E33" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F33" s="38"/>
       <c r="G33" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="92" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B34" s="30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C34" s="30">
         <v>2E-3</v>
@@ -2102,19 +2102,19 @@
         <v>13</v>
       </c>
       <c r="E34" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F34" s="38"/>
       <c r="G34" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="92" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B35" s="30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C35" s="30">
         <v>2E-3</v>
@@ -2123,19 +2123,19 @@
         <v>13</v>
       </c>
       <c r="E35" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F35" s="38"/>
       <c r="G35" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="92" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B36" s="30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C36" s="30">
         <v>2E-3</v>
@@ -2144,19 +2144,19 @@
         <v>13</v>
       </c>
       <c r="E36" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F36" s="38"/>
       <c r="G36" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="92" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" s="30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C37" s="30">
         <v>2E-3</v>
@@ -2165,19 +2165,19 @@
         <v>13</v>
       </c>
       <c r="E37" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="F37" s="38"/>
       <c r="G37" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="92" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B38" s="30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C38" s="30">
         <v>2E-3</v>
@@ -2186,19 +2186,19 @@
         <v>13</v>
       </c>
       <c r="E38" s="33" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F38" s="38"/>
       <c r="G38" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="92" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C39" s="30">
         <v>2E-3</v>
@@ -2207,19 +2207,19 @@
         <v>13</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F39" s="38"/>
       <c r="G39" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="92" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" s="30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C40" s="30">
         <v>2E-3</v>
@@ -2228,19 +2228,19 @@
         <v>13</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F40" s="57"/>
       <c r="G40" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A41" s="58" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B41" s="59" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C41" s="60">
         <v>0.88</v>
@@ -2249,19 +2249,19 @@
         <v>13</v>
       </c>
       <c r="E41" s="61" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F41" s="38"/>
       <c r="G41" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A42" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C42" s="55">
         <v>0.05</v>
@@ -2270,19 +2270,19 @@
         <v>13</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F42" s="38"/>
       <c r="G42" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A43" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C43" s="55">
         <v>0.43</v>
@@ -2291,19 +2291,19 @@
         <v>13</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F43" s="38"/>
       <c r="G43" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C44" s="55">
         <v>0.69</v>
@@ -2312,19 +2312,19 @@
         <v>13</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F44" s="49"/>
       <c r="G44" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A45" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C45" s="55">
         <v>0.42</v>
@@ -2333,19 +2333,19 @@
         <v>13</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F45" s="50"/>
       <c r="G45" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A46" s="21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C46" s="55">
         <v>0</v>
@@ -2354,19 +2354,19 @@
         <v>13</v>
       </c>
       <c r="E46" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F46" s="50"/>
       <c r="G46" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A47" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C47" s="55">
         <v>0.25</v>
@@ -2375,19 +2375,19 @@
         <v>13</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F47" s="38"/>
       <c r="G47" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C48" s="22">
         <v>0</v>
@@ -2396,19 +2396,19 @@
         <v>13</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F48" s="38"/>
       <c r="G48" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C49" s="22">
         <v>0.04</v>
@@ -2417,19 +2417,19 @@
         <v>13</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F49" s="38"/>
       <c r="G49" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C50" s="22">
         <v>0.42</v>
@@ -2438,19 +2438,19 @@
         <v>13</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F50" s="38"/>
       <c r="G50" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C51" s="22">
         <v>0.42</v>
@@ -2459,19 +2459,19 @@
         <v>13</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F51" s="38"/>
       <c r="G51" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C52" s="22">
         <v>0.25</v>
@@ -2480,19 +2480,19 @@
         <v>13</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F52" s="49"/>
       <c r="G52" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C53" s="22">
         <v>0.25</v>
@@ -2501,19 +2501,19 @@
         <v>13</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F53" s="50"/>
       <c r="G53" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C54" s="22">
         <v>0.25</v>
@@ -2522,19 +2522,19 @@
         <v>13</v>
       </c>
       <c r="E54" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F54" s="38"/>
       <c r="G54" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="53" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C55" s="23">
         <v>0.25</v>
@@ -2543,19 +2543,19 @@
         <v>13</v>
       </c>
       <c r="E55" s="20" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F55" s="38"/>
       <c r="G55" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B56" s="35" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C56" s="51">
         <v>0.46</v>
@@ -2564,19 +2564,19 @@
         <v>13</v>
       </c>
       <c r="E56" s="52" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F56" s="38"/>
       <c r="G56" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B57" s="30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C57" s="31">
         <v>0.02</v>
@@ -2585,19 +2585,19 @@
         <v>13</v>
       </c>
       <c r="E57" s="33" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F57" s="38"/>
       <c r="G57" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B58" s="30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C58" s="31">
         <v>0.23</v>
@@ -2606,15 +2606,15 @@
         <v>13</v>
       </c>
       <c r="E58" s="33" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B59" s="30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C59" s="31">
         <v>0.36</v>
@@ -2623,15 +2623,15 @@
         <v>13</v>
       </c>
       <c r="E59" s="33" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A60" s="36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B60" s="30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C60" s="42">
         <v>0.22</v>
@@ -2640,15 +2640,15 @@
         <v>13</v>
       </c>
       <c r="E60" s="33" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A61" s="36" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C61" s="42">
         <v>0</v>
@@ -2657,15 +2657,15 @@
         <v>13</v>
       </c>
       <c r="E61" s="33" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A62" s="36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B62" s="30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C62" s="42">
         <v>0.13</v>
@@ -2674,15 +2674,15 @@
         <v>13</v>
       </c>
       <c r="E62" s="33" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A63" s="36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B63" s="30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C63" s="42">
         <v>0</v>
@@ -2691,15 +2691,15 @@
         <v>13</v>
       </c>
       <c r="E63" s="33" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15" x14ac:dyDescent="0.3">
       <c r="A64" s="36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B64" s="30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C64" s="42">
         <v>0.02</v>
@@ -2708,15 +2708,15 @@
         <v>13</v>
       </c>
       <c r="E64" s="33" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A65" s="36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B65" s="30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C65" s="42">
         <v>0</v>
@@ -2725,15 +2725,15 @@
         <v>13</v>
       </c>
       <c r="E65" s="33" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="44" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B66" s="43" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C66" s="43">
         <v>0.8</v>
@@ -2742,15 +2742,15 @@
         <v>13</v>
       </c>
       <c r="E66" s="45" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="44" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B67" s="43" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C67" s="43">
         <v>0.18</v>
@@ -2759,15 +2759,15 @@
         <v>13</v>
       </c>
       <c r="E67" s="45" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="44" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B68" s="43" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C68" s="43">
         <v>0.18</v>
@@ -2776,15 +2776,15 @@
         <v>13</v>
       </c>
       <c r="E68" s="45" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B69" s="43" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C69" s="43">
         <v>0.8</v>
@@ -2793,15 +2793,15 @@
         <v>13</v>
       </c>
       <c r="E69" s="45" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="46" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B70" s="47" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C70" s="47">
         <v>0.18</v>
@@ -2810,15 +2810,15 @@
         <v>13</v>
       </c>
       <c r="E70" s="48" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="39" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B71" s="40" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C71" s="40">
         <v>6.0000000000000001E-3</v>
@@ -2827,15 +2827,15 @@
         <v>13</v>
       </c>
       <c r="E71" s="41" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="25" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B72" s="24" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C72" s="24">
         <v>7.9000000000000001E-2</v>
@@ -2844,15 +2844,15 @@
         <v>13</v>
       </c>
       <c r="E72" s="26" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="25" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B73" s="24" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C73" s="24">
         <v>2.1999999999999999E-2</v>
@@ -2861,15 +2861,15 @@
         <v>13</v>
       </c>
       <c r="E73" s="26" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B74" s="28" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C74" s="28">
         <v>0.80700000000000005</v>
@@ -2878,15 +2878,15 @@
         <v>13</v>
       </c>
       <c r="E74" s="29" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="80" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B75" s="81" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C75" s="82">
         <v>0.23169999999999999</v>
@@ -2895,15 +2895,15 @@
         <v>14</v>
       </c>
       <c r="E75" s="83" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="84" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B76" s="85" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C76" s="86">
         <v>0.23169999999999999</v>
@@ -2912,15 +2912,15 @@
         <v>14</v>
       </c>
       <c r="E76" s="87" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="84" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B77" s="85" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C77" s="86">
         <v>0.23169999999999999</v>
@@ -2929,15 +2929,15 @@
         <v>14</v>
       </c>
       <c r="E77" s="87" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="84" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B78" s="85" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C78" s="86">
         <v>0.23169999999999999</v>
@@ -2946,15 +2946,15 @@
         <v>14</v>
       </c>
       <c r="E78" s="87" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="84" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B79" s="85" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C79" s="86">
         <v>0.23169999999999999</v>
@@ -2963,15 +2963,15 @@
         <v>14</v>
       </c>
       <c r="E79" s="87" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="84" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B80" s="85" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C80" s="86">
         <v>0.23169999999999999</v>
@@ -2980,15 +2980,15 @@
         <v>14</v>
       </c>
       <c r="E80" s="87" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="84" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B81" s="85" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C81" s="86">
         <v>0.23169999999999999</v>
@@ -2997,15 +2997,15 @@
         <v>14</v>
       </c>
       <c r="E81" s="87" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="84" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B82" s="85" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C82" s="86">
         <v>0.23169999999999999</v>
@@ -3014,15 +3014,15 @@
         <v>14</v>
       </c>
       <c r="E82" s="87" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="75" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B83" s="76" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C83" s="77">
         <v>1.06E-2</v>
@@ -3031,15 +3031,15 @@
         <v>14</v>
       </c>
       <c r="E83" s="78" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B84" s="35" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C84" s="64">
         <v>1.06E-2</v>
@@ -3048,15 +3048,15 @@
         <v>14</v>
       </c>
       <c r="E84" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B85" s="35" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C85" s="64">
         <v>1.06E-2</v>
@@ -3065,15 +3065,15 @@
         <v>14</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B86" s="35" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C86" s="64">
         <v>1.06E-2</v>
@@ -3082,15 +3082,15 @@
         <v>14</v>
       </c>
       <c r="E86" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B87" s="35" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C87" s="64">
         <v>1.06E-2</v>
@@ -3099,15 +3099,15 @@
         <v>14</v>
       </c>
       <c r="E87" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B88" s="35" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C88" s="64">
         <v>1.06E-2</v>
@@ -3116,15 +3116,15 @@
         <v>14</v>
       </c>
       <c r="E88" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B89" s="35" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C89" s="64">
         <v>1.06E-2</v>
@@ -3133,15 +3133,15 @@
         <v>14</v>
       </c>
       <c r="E89" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B90" s="35" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C90" s="64">
         <v>1.06E-2</v>
@@ -3150,15 +3150,15 @@
         <v>14</v>
       </c>
       <c r="E90" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B91" s="35" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C91" s="64">
         <v>1.06E-2</v>
@@ -3167,15 +3167,15 @@
         <v>14</v>
       </c>
       <c r="E91" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A92" s="80" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B92" s="81" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C92" s="88">
         <v>0.88</v>
@@ -3184,15 +3184,15 @@
         <v>14</v>
       </c>
       <c r="E92" s="83" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="89" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B93" s="90" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C93" s="90">
         <v>6.0000000000000001E-3</v>
@@ -3201,15 +3201,15 @@
         <v>14</v>
       </c>
       <c r="E93" s="91" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="54" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C94" s="62">
         <v>0.23169999999999999</v>
@@ -3218,15 +3218,15 @@
         <v>15</v>
       </c>
       <c r="E94" s="16" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B95" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C95" s="63">
         <v>0.23169999999999999</v>
@@ -3235,15 +3235,15 @@
         <v>15</v>
       </c>
       <c r="E95" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C96" s="63">
         <v>0.23169999999999999</v>
@@ -3252,15 +3252,15 @@
         <v>15</v>
       </c>
       <c r="E96" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B97" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C97" s="63">
         <v>0.23169999999999999</v>
@@ -3269,15 +3269,15 @@
         <v>15</v>
       </c>
       <c r="E97" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C98" s="63">
         <v>0.23169999999999999</v>
@@ -3286,15 +3286,15 @@
         <v>15</v>
       </c>
       <c r="E98" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B99" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C99" s="63">
         <v>0.23169999999999999</v>
@@ -3303,15 +3303,15 @@
         <v>15</v>
       </c>
       <c r="E99" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B100" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C100" s="63">
         <v>0.23169999999999999</v>
@@ -3320,15 +3320,15 @@
         <v>15</v>
       </c>
       <c r="E100" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B101" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C101" s="63">
         <v>0.23169999999999999</v>
@@ -3337,15 +3337,15 @@
         <v>15</v>
       </c>
       <c r="E101" s="18" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="75" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B102" s="76" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C102" s="77">
         <v>1.06E-2</v>
@@ -3354,15 +3354,15 @@
         <v>15</v>
       </c>
       <c r="E102" s="78" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B103" s="35" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C103" s="64">
         <v>1.06E-2</v>
@@ -3371,15 +3371,15 @@
         <v>15</v>
       </c>
       <c r="E103" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B104" s="35" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C104" s="64">
         <v>1.06E-2</v>
@@ -3388,15 +3388,15 @@
         <v>15</v>
       </c>
       <c r="E104" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B105" s="35" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C105" s="64">
         <v>1.06E-2</v>
@@ -3405,15 +3405,15 @@
         <v>15</v>
       </c>
       <c r="E105" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B106" s="35" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C106" s="64">
         <v>1.06E-2</v>
@@ -3422,15 +3422,15 @@
         <v>15</v>
       </c>
       <c r="E106" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B107" s="35" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C107" s="64">
         <v>1.06E-2</v>
@@ -3439,15 +3439,15 @@
         <v>15</v>
       </c>
       <c r="E107" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B108" s="35" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C108" s="64">
         <v>1.06E-2</v>
@@ -3456,15 +3456,15 @@
         <v>15</v>
       </c>
       <c r="E108" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B109" s="35" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C109" s="64">
         <v>1.06E-2</v>
@@ -3473,15 +3473,15 @@
         <v>15</v>
       </c>
       <c r="E109" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B110" s="35" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C110" s="64">
         <v>1.06E-2</v>
@@ -3490,15 +3490,15 @@
         <v>15</v>
       </c>
       <c r="E110" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="75" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B111" s="76" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C111" s="77">
         <v>1.06E-2</v>
@@ -3507,15 +3507,15 @@
         <v>15</v>
       </c>
       <c r="E111" s="78" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B112" s="35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C112" s="64">
         <v>1.06E-2</v>
@@ -3524,15 +3524,15 @@
         <v>15</v>
       </c>
       <c r="E112" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B113" s="35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C113" s="64">
         <v>1.06E-2</v>
@@ -3541,15 +3541,15 @@
         <v>15</v>
       </c>
       <c r="E113" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B114" s="35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C114" s="64">
         <v>1.06E-2</v>
@@ -3558,15 +3558,15 @@
         <v>15</v>
       </c>
       <c r="E114" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B115" s="35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C115" s="64">
         <v>1.06E-2</v>
@@ -3575,15 +3575,15 @@
         <v>15</v>
       </c>
       <c r="E115" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B116" s="35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C116" s="64">
         <v>1.06E-2</v>
@@ -3592,15 +3592,15 @@
         <v>15</v>
       </c>
       <c r="E116" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B117" s="35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C117" s="64">
         <v>1.06E-2</v>
@@ -3609,15 +3609,15 @@
         <v>15</v>
       </c>
       <c r="E117" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B118" s="35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C118" s="64">
         <v>1.06E-2</v>
@@ -3626,15 +3626,15 @@
         <v>15</v>
       </c>
       <c r="E118" s="33" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B119" s="79" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C119" s="65">
         <v>1.06E-2</v>
@@ -3643,15 +3643,15 @@
         <v>15</v>
       </c>
       <c r="E119" s="56" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A120" s="58" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B120" s="59" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C120" s="60">
         <v>0.88</v>
@@ -3660,15 +3660,15 @@
         <v>15</v>
       </c>
       <c r="E120" s="61" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A121" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B121" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C121" s="55">
         <v>0.05</v>
@@ -3677,15 +3677,15 @@
         <v>15</v>
       </c>
       <c r="E121" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A122" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B122" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C122" s="55">
         <v>0.43</v>
@@ -3694,15 +3694,15 @@
         <v>15</v>
       </c>
       <c r="E122" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A123" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B123" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C123" s="55">
         <v>0.69</v>
@@ -3711,15 +3711,15 @@
         <v>15</v>
       </c>
       <c r="E123" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A124" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B124" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C124" s="55">
         <v>0.42</v>
@@ -3728,15 +3728,15 @@
         <v>15</v>
       </c>
       <c r="E124" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A125" s="21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B125" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C125" s="55">
         <v>0</v>
@@ -3745,15 +3745,15 @@
         <v>15</v>
       </c>
       <c r="E125" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A126" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B126" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C126" s="55">
         <v>0.25</v>
@@ -3762,15 +3762,15 @@
         <v>15</v>
       </c>
       <c r="E126" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B127" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C127" s="22">
         <v>0</v>
@@ -3779,15 +3779,15 @@
         <v>15</v>
       </c>
       <c r="E127" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B128" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C128" s="22">
         <v>0.04</v>
@@ -3796,15 +3796,15 @@
         <v>15</v>
       </c>
       <c r="E128" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B129" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C129" s="22">
         <v>0.42</v>
@@ -3813,15 +3813,15 @@
         <v>15</v>
       </c>
       <c r="E129" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B130" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C130" s="22">
         <v>0.42</v>
@@ -3830,15 +3830,15 @@
         <v>15</v>
       </c>
       <c r="E130" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C131" s="22">
         <v>0.25</v>
@@ -3847,15 +3847,15 @@
         <v>15</v>
       </c>
       <c r="E131" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C132" s="22">
         <v>0.25</v>
@@ -3864,15 +3864,15 @@
         <v>15</v>
       </c>
       <c r="E132" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C133" s="22">
         <v>0.25</v>
@@ -3881,15 +3881,15 @@
         <v>15</v>
       </c>
       <c r="E133" s="18" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="53" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B134" s="19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C134" s="23">
         <v>0.25</v>
@@ -3898,15 +3898,15 @@
         <v>15</v>
       </c>
       <c r="E134" s="20" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B135" s="35" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C135" s="51">
         <v>0.46</v>
@@ -3915,15 +3915,15 @@
         <v>15</v>
       </c>
       <c r="E135" s="52" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B136" s="30" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C136" s="31">
         <v>0.02</v>
@@ -3932,15 +3932,15 @@
         <v>15</v>
       </c>
       <c r="E136" s="33" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B137" s="30" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C137" s="31">
         <v>0.23</v>
@@ -3949,15 +3949,15 @@
         <v>15</v>
       </c>
       <c r="E137" s="33" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B138" s="30" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C138" s="31">
         <v>0.36</v>
@@ -3966,15 +3966,15 @@
         <v>15</v>
       </c>
       <c r="E138" s="33" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A139" s="36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B139" s="30" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C139" s="42">
         <v>0.22</v>
@@ -3983,15 +3983,15 @@
         <v>15</v>
       </c>
       <c r="E139" s="33" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A140" s="36" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B140" s="30" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C140" s="42">
         <v>0</v>
@@ -4000,15 +4000,15 @@
         <v>15</v>
       </c>
       <c r="E140" s="33" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A141" s="36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B141" s="30" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C141" s="42">
         <v>0.13</v>
@@ -4017,15 +4017,15 @@
         <v>15</v>
       </c>
       <c r="E141" s="33" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A142" s="36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B142" s="30" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C142" s="42">
         <v>0</v>
@@ -4034,15 +4034,15 @@
         <v>15</v>
       </c>
       <c r="E142" s="33" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A143" s="36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B143" s="30" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C143" s="42">
         <v>0.02</v>
@@ -4051,15 +4051,15 @@
         <v>15</v>
       </c>
       <c r="E143" s="33" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="15" x14ac:dyDescent="0.3">
       <c r="A144" s="36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B144" s="30" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C144" s="42">
         <v>0</v>
@@ -4068,15 +4068,15 @@
         <v>15</v>
       </c>
       <c r="E144" s="33" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="44" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B145" s="43" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C145" s="43">
         <v>0.8</v>
@@ -4085,15 +4085,15 @@
         <v>15</v>
       </c>
       <c r="E145" s="45" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="44" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B146" s="43" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C146" s="43">
         <v>0.18</v>
@@ -4102,15 +4102,15 @@
         <v>15</v>
       </c>
       <c r="E146" s="45" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="44" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B147" s="43" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C147" s="43">
         <v>0.18</v>
@@ -4119,15 +4119,15 @@
         <v>15</v>
       </c>
       <c r="E147" s="45" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B148" s="43" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C148" s="43">
         <v>0.8</v>
@@ -4136,15 +4136,15 @@
         <v>15</v>
       </c>
       <c r="E148" s="45" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="46" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B149" s="47" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C149" s="47">
         <v>0.18</v>
@@ -4153,15 +4153,15 @@
         <v>15</v>
       </c>
       <c r="E149" s="48" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="89" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B150" s="90" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C150" s="90">
         <v>6.0000000000000001E-3</v>
@@ -4170,46 +4170,46 @@
         <v>15</v>
       </c>
       <c r="E150" s="91" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="89" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B151" s="90" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C151" s="90">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="D151" s="90" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E151" s="91" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="89" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B152" s="90" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C152" s="90">
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="D152" s="90" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E152" s="91" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D153" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -4224,7 +4224,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D35B896B-BFBE-403F-A891-C25041EF70AE}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.88671875" bestFit="1" customWidth="1"/>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" s="11">
         <v>1</v>
@@ -4272,7 +4272,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
@@ -4287,7 +4287,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2E14F0C-085B-4F8B-80A4-853CC51FC5EB}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.109375" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
@@ -4316,8 +4316,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B8F814574E960A4499025803604D4DF4" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="314e7041d7d1561dbe33e80becf1c782">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b2ff61d-e0c4-454b-ba72-44cf85c32a41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="84c838da6aa04a0f137f8b0aba02cfe1" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B8F814574E960A4499025803604D4DF4" ma:contentTypeVersion="9" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="613b0908c48a25395136f5b5d1e9264a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4b2ff61d-e0c4-454b-ba72-44cf85c32a41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f5652efc65d8021725ff526b59607fd6" ns2:_="">
     <xsd:import namespace="4b2ff61d-e0c4-454b-ba72-44cf85c32a41"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -4395,8 +4395,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -4486,12 +4486,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4500,25 +4494,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{256506D4-E644-4579-8C9D-2DF223E5A027}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39E50AB6-F6C1-4D80-973E-E2E606121922}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69F79AB8-49D9-484F-991A-27FAE0E62C64}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4b2ff61d-e0c4-454b-ba72-44cf85c32a41"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EC1CB49-63A2-4BB9-A6E1-B93BAD25C62D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -4526,12 +4520,4 @@
     <ds:schemaRef ds:uri="9c2c21c4-f980-47d5-be5b-1bb924ee96a2"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69F79AB8-49D9-484F-991A-27FAE0E62C64}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>